--- a/out/LSTM-Mamba1_repeat_1_000007.xlsx
+++ b/out/LSTM-Mamba1_repeat_1_000007.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.5195375025212516</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.5195375025212516</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>9.227858435864231</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>9.227858435864231</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>9.227858435864231</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.0804624974787484</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.0804624974787484</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
-        <v>-6.038105188275221e-05</v>
+        <v>-6.75351114863297e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.6961042754547568</v>
+        <v>0.7785800168151985</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.393284754049746</v>
+        <v>1.558363729382479</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1043839412694196</v>
+        <v>0.1167515465921939</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
-        <v>0.9050139873536248</v>
+        <v>1.012241738182021</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1305139476654237</v>
+        <v>0.1459774784774187</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.061674472939382</v>
+        <v>1.18746364413097</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.1870911250288232</v>
+        <v>0.209257860438623</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.305416430128927</v>
+        <v>1.460084593687064</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2001504448110093</v>
+        <v>0.2238644609173098</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
-        <v>1.518640143900103</v>
+        <v>1.698571628299907</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2121183915624241</v>
+        <v>0.237251944347076</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.742743104207468</v>
+        <v>1.949227299831098</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.09572575083263495</v>
+        <v>0.1070667240257002</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.721898468050247</v>
+        <v>1.925912980847788</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.04623051919669491</v>
+        <v>0.05170897721724928</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.71855998084306</v>
+        <v>1.922178923545358</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02202746602705347</v>
+        <v>0.02463717527422079</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.716347619634103</v>
+        <v>1.919704459501471</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.006523580880987169</v>
+        <v>0.007297419349351257</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.707346355452162</v>
+        <v>1.909637419604475</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.004313887701662389</v>
+        <v>0.004825271689484421</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.709447096823808</v>
+        <v>1.911987494252265</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002204963193759101</v>
+        <v>0.002466695254996821</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.709541551479308</v>
+        <v>1.912093724905556</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001125481580367856</v>
+        <v>0.001259367644650069</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.709586259537464</v>
+        <v>1.912144317334213</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0004203693234568383</v>
+        <v>0.0004703237279909154</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.70929965271882</v>
+        <v>1.911824389174857</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002268266796096673</v>
+        <v>0.0002540518768592011</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.709332699793215</v>
+        <v>1.911861972613917</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.000106262193078166</v>
+        <v>0.0001197726022376576</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.709319046125635</v>
+        <v>1.911847271824636</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>6.387685822045283e-05</v>
+        <v>7.273245427736819e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.70934067507415</v>
+        <v>1.911872110684413</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.10279205119908e-05</v>
+        <v>3.514539714193261e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.709338859507548</v>
+        <v>1.911870653856644</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.29836763541332e-05</v>
+        <v>1.498186261570356e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.709332746370905</v>
+        <v>1.911864417038152</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>6.512317399864405e-06</v>
+        <v>7.791463777627117e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.709332779412467</v>
+        <v>1.911865009306555</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-3.375548894532629e-07</v>
+        <v>8.280563881834207e-07</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.70932675070418</v>
+        <v>1.911858865510579</v>
       </c>
     </row>
     <row r="61">
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.709321066170152</v>
+        <v>1.911853180976551</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.709316314894938</v>
+        <v>1.911848429701337</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.709311025747376</v>
+        <v>1.911843140553775</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.709311003013075</v>
+        <v>1.911843117819474</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.709311321293292</v>
+        <v>1.91184343609969</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.709312412539749</v>
+        <v>1.911844527346148</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.709311722932613</v>
+        <v>1.911843837739012</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.709311753245014</v>
+        <v>1.911843868051413</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.709311563792504</v>
+        <v>1.911843678598903</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.709311616839207</v>
+        <v>1.911843731645606</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.70931166988591</v>
+        <v>1.911843784692309</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.709311631995408</v>
+        <v>1.911843746801807</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.709311503167702</v>
+        <v>1.9118436179741</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.709311359183794</v>
+        <v>1.911843473990193</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.709311200043685</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.709311253090388</v>
+        <v>1.911843367896787</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.709311200043685</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.709311200043685</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.709311018169276</v>
+        <v>1.911843132975675</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.709311184887485</v>
+        <v>1.911843299693883</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.709311381918095</v>
+        <v>1.911843496724494</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.709311222777987</v>
+        <v>1.911843337584386</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.709311260668489</v>
+        <v>1.911843375474887</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.709311457699099</v>
+        <v>1.911843572505498</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.709311434964798</v>
+        <v>1.911843549771197</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.70931128340279</v>
+        <v>1.911843398209189</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.709311207621786</v>
+        <v>1.911843322428185</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.709311306137091</v>
+        <v>1.91184342094349</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.709311313715192</v>
+        <v>1.91184342852159</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.709311578948705</v>
+        <v>1.911843693755104</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.70931128340279</v>
+        <v>1.911843398209189</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.709311525902003</v>
+        <v>1.911843640708401</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.709311609261107</v>
+        <v>1.911843724067505</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.709311442542898</v>
+        <v>1.911843557349297</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.709311631995408</v>
+        <v>1.911843746801807</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.70931128340279</v>
+        <v>1.911843398209189</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.709311078794079</v>
+        <v>1.911843193600478</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.709311192465585</v>
+        <v>1.911843307271984</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.709311207621786</v>
+        <v>1.911843322428185</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.709310972700674</v>
+        <v>1.911843087507072</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.709311033325477</v>
+        <v>1.911843148131875</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.70931090449777</v>
+        <v>1.911843019304169</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.709311040903577</v>
+        <v>1.911843155709976</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.709311215199886</v>
+        <v>1.911843330006285</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.709311359183794</v>
+        <v>1.911843473990193</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.709311192465585</v>
+        <v>1.911843307271984</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.709311184887485</v>
+        <v>1.911843299693883</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.70931089691967</v>
+        <v>1.911843011726068</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.709310912075871</v>
+        <v>1.911843026882269</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.709311139418882</v>
+        <v>1.911843254225281</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.709311124262682</v>
+        <v>1.91184323906908</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.709311230356087</v>
+        <v>1.911843345162486</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.709310957544473</v>
+        <v>1.911843072350872</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.709311056059778</v>
+        <v>1.911843170866177</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.709311207621786</v>
+        <v>1.911843322428185</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.709311222777987</v>
+        <v>1.911843337584386</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.709311200043685</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.70931128340279</v>
+        <v>1.911843398209189</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.709311381918095</v>
+        <v>1.911843496724494</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.709311215199886</v>
+        <v>1.911843330006285</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.709311200043685</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.709311169731284</v>
+        <v>1.911843284537683</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.709311154575083</v>
+        <v>1.911843269381482</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.709311192465585</v>
+        <v>1.911843307271984</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.709311207621786</v>
+        <v>1.911843322428185</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.709311200043685</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_1_000007.xlsx
+++ b/out/LSTM-Mamba1_repeat_1_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.5195375025212516</v>
+        <v>1.019639998847428</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>9.227858435864231</v>
+        <v>2.029819999423714</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>9.227858435864231</v>
+        <v>3.04</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>9.227858435864231</v>
+        <v>2.029819999423714</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.0804624974787484</v>
+        <v>1.019639998847428</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.0804624974787484</v>
+        <v>0.009459998271141773</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC39" t="n">
-        <v>-6.038105188275221e-05</v>
+        <v>-8.546977557591163e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.6961042754547568</v>
+        <v>0.9853402816245017</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.393284754049746</v>
+        <v>1.97220372150127</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1043839412694196</v>
+        <v>0.147756147921141</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC41" t="n">
-        <v>0.9050139873536248</v>
+        <v>1.281053318952219</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1305139476654237</v>
+        <v>0.1847432616428064</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.061674472939382</v>
+        <v>1.502807227226318</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.1870911250288232</v>
+        <v>0.2648285894382127</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.305416430128927</v>
+        <v>1.847825615446181</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2001504448110093</v>
+        <v>0.2833144815687005</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC44" t="n">
-        <v>1.518640143900103</v>
+        <v>2.149645408963376</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2121183915624241</v>
+        <v>0.3002555080376145</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.742743104207468</v>
+        <v>2.466864858485233</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.09572575083263495</v>
+        <v>0.1355003922555187</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.721898468050247</v>
+        <v>2.437359147104967</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.04623051919669491</v>
+        <v>0.06544049620513794</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.71855998084306</v>
+        <v>2.432633496436944</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02202746602705347</v>
+        <v>0.03118044815415464</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.716347619634103</v>
+        <v>2.429501927713564</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.006523580880987169</v>
+        <v>0.009236011869159132</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.707346355452162</v>
+        <v>2.41676319139874</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.004313887701662389</v>
+        <v>0.00610757665142914</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.709447096823808</v>
+        <v>2.419738708844289</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002204963193759101</v>
+        <v>0.003123977273443428</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.709541551479308</v>
+        <v>2.419874489569761</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001125481580367856</v>
+        <v>0.001595592798561791</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.709586259537464</v>
+        <v>2.419939836555451</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0004203693234568383</v>
+        <v>0.000596723509160474</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.70929965271882</v>
+        <v>2.419536478155412</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002268266796096673</v>
+        <v>0.0003225273729716651</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.709332699793215</v>
+        <v>2.419585299698297</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.000106262193078166</v>
+        <v>0.0001531512601611074</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.709319046125635</v>
+        <v>2.419568042214864</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>6.387685822045283e-05</v>
+        <v>9.2411556626069e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.70934067507415</v>
+        <v>2.419600624668867</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.10279205119908e-05</v>
+        <v>4.646845787427258e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.709338859507548</v>
+        <v>2.419600108904289</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.29836763541332e-05</v>
+        <v>1.997732826962944e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.709332746370905</v>
+        <v>2.419593562881174</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>6.512317399864405e-06</v>
+        <v>1.034975653315254e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.709332779412467</v>
+        <v>2.419595553992971</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-3.375548894532629e-07</v>
+        <v>1.993667665820105e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.70932675070418</v>
+        <v>2.419589067766295</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-2.941261685029097e-06</v>
+        <v>-1.911892527543644e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.709321066170152</v>
+        <v>2.419583109168156</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-3.887371769088796e-06</v>
+        <v>-2.77474353817759e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.709316314894938</v>
+        <v>2.419578439899519</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.709311025747376</v>
+        <v>2.419573150751957</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.709311003013075</v>
+        <v>2.419573128017656</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.709311321293292</v>
+        <v>2.419573446297872</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.709312412539749</v>
+        <v>2.419574537544329</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.709311722932613</v>
+        <v>2.419573847937193</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.709311753245014</v>
+        <v>2.419573878249595</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.709311563792504</v>
+        <v>2.419573688797084</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.709311616839207</v>
+        <v>2.419573741843787</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.70931166988591</v>
+        <v>2.419573794890491</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.709311631995408</v>
+        <v>2.419573756999988</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.709311503167702</v>
+        <v>2.419573628172281</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.709311359183794</v>
+        <v>2.419573484188374</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.709311200043685</v>
+        <v>2.419573325048265</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.709311253090388</v>
+        <v>2.419573378094968</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.709311200043685</v>
+        <v>2.419573325048265</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.709311200043685</v>
+        <v>2.419573325048265</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.709311018169276</v>
+        <v>2.419573143173856</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.709311184887485</v>
+        <v>2.419573309892065</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.709311381918095</v>
+        <v>2.419573506922675</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.709311222777987</v>
+        <v>2.419573347782567</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.709311260668489</v>
+        <v>2.419573385673069</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.709311457699099</v>
+        <v>2.419573582703679</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.709311434964798</v>
+        <v>2.419573559969378</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.70931128340279</v>
+        <v>2.41957340840737</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.709311207621786</v>
+        <v>2.419573332626366</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.709311306137091</v>
+        <v>2.419573431141671</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.709311313715192</v>
+        <v>2.419573438719772</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.709311578948705</v>
+        <v>2.419573703953286</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.70931128340279</v>
+        <v>2.41957340840737</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.709311525902003</v>
+        <v>2.419573650906583</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.709311609261107</v>
+        <v>2.419573734265687</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.709311442542898</v>
+        <v>2.419573567547478</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.709311631995408</v>
+        <v>2.419573756999988</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.70931128340279</v>
+        <v>2.41957340840737</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.709311078794079</v>
+        <v>2.419573203798659</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.709311192465585</v>
+        <v>2.419573317470165</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.709311207621786</v>
+        <v>2.419573332626366</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.709310972700674</v>
+        <v>2.419573097705254</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.709311033325477</v>
+        <v>2.419573158330057</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.70931090449777</v>
+        <v>2.419573029502351</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.709311040903577</v>
+        <v>2.419573165908157</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.709311215199886</v>
+        <v>2.419573340204467</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.709311359183794</v>
+        <v>2.419573484188374</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.709311192465585</v>
+        <v>2.419573317470165</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.709311184887485</v>
+        <v>2.419573309892065</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.70931089691967</v>
+        <v>2.41957302192425</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.709310912075871</v>
+        <v>2.419573037080451</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.709311139418882</v>
+        <v>2.419573264423462</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.709311124262682</v>
+        <v>2.419573249267262</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.709311230356087</v>
+        <v>2.419573355360667</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.709310957544473</v>
+        <v>2.419573082549053</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.709311056059778</v>
+        <v>2.419573181064358</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.709311207621786</v>
+        <v>2.419573332626366</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.709311222777987</v>
+        <v>2.419573347782567</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.709311200043685</v>
+        <v>2.419573325048265</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.70931128340279</v>
+        <v>2.41957340840737</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.709311381918095</v>
+        <v>2.419573506922675</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.709311215199886</v>
+        <v>2.419573340204467</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.709311200043685</v>
+        <v>2.419573325048265</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.709311169731284</v>
+        <v>2.419573294735864</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.709311154575083</v>
+        <v>2.419573279579663</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.709311192465585</v>
+        <v>2.419573317470165</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.709311207621786</v>
+        <v>2.419573332626366</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.709311200043685</v>
+        <v>2.419573325048265</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_1_000007.xlsx
+++ b/out/LSTM-Mamba1_repeat_1_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.007550928276032209</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-1.28</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.004569283686578274</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.8599999999999997</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.002942008897662163</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.002032063901424408</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.16</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.001496887765824795</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.001181662082672119</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.0009840475395321846</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.0008318424224853516</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.0006994428113102913</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.0005995491519570351</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.0005179233849048615</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.0004509929567575455</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.0003774473443627357</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.0003381473943591118</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.0002913353964686394</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.0002347761765122414</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.0001595616340637207</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.0001011621206998825</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-2.728216350078583e-05</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.019639998847428</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>5.280692130327225e-05</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.029819999423714</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.0001017004251480103</v>
       </c>
       <c r="JB22" t="n">
-        <v>3.04</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.0001066382974386215</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.029819999423714</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-5.587935447692871e-08</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.019639998847428</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.0001111077144742012</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.009459998271141773</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.0001940708607435226</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.16</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.0002483353018760681</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.0002760998904705048</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.0002594385296106339</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.000296187587082386</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.0003367029130458832</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.0003795046359300613</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.0004108911380171776</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.0004037357866764069</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.0003892546519637108</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.0003645466640591621</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.0003487421199679375</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.0005714474245905876</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.0008577350527048111</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
-        <v>-8.546977557591163e-05</v>
+        <v>-3.441802114946768e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.9853402816245017</v>
+        <v>0.3967888760374763</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.001155446283519268</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.97220372150127</v>
+        <v>0.7941912676247608</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.147756147921141</v>
+        <v>0.0595002846383187</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.001379312016069889</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.281053318952219</v>
+        <v>0.5158702640959101</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1847432616428064</v>
+        <v>0.07439471593848709</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.001551940105855465</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.502807227226318</v>
+        <v>0.6051688603947142</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.2648285894382127</v>
+        <v>0.1066444724881971</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.001666946336627007</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.847825615446181</v>
+        <v>0.744105073663596</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2833144815687005</v>
+        <v>0.114088461448183</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.001851177774369717</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>2.149645408963376</v>
+        <v>0.8656454752919374</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3002555080376145</v>
+        <v>0.1209107735406293</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.00222381018102169</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>2.466864858485233</v>
+        <v>0.9933871939977117</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1355003922555187</v>
+        <v>0.05456478330665339</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.002675746567547321</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>2.437359147104967</v>
+        <v>0.981505510697955</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.06544049620513794</v>
+        <v>0.02635165320710885</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.003212705254554749</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>2.432633496436944</v>
+        <v>0.9796025348604981</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.03118044815415464</v>
+        <v>0.01255459099981437</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.003545243293046951</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>2.429501927713564</v>
+        <v>0.9783402633769335</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.009236011869159132</v>
+        <v>0.003716690737052452</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.003660714253783226</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.41676319139874</v>
+        <v>0.9732071272224644</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.00610757665142914</v>
+        <v>0.002456756377466587</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.003669597208499908</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.419738708844289</v>
+        <v>0.974402395117587</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.003123977273443428</v>
+        <v>0.001254462550316852</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.003657129593193531</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.419874489569761</v>
+        <v>0.9744540843074243</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001595592798561791</v>
+        <v>0.0006392637679745575</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.003572961315512657</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.419939836555451</v>
+        <v>0.9744774228095501</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.000596723509160474</v>
+        <v>0.0002372031734985556</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.003445684909820557</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.419536478155412</v>
+        <v>0.9743118272127244</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003225273729716651</v>
+        <v>0.0001270009563613764</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.003341276198625565</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.419585299698297</v>
+        <v>0.9743285592302303</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001531512601611074</v>
+        <v>5.857839604466628e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.003245980478823185</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.419568042214864</v>
+        <v>0.9743186012862977</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>9.2411556626069e-05</v>
+        <v>3.435820469740162e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.003205060958862305</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.419600624668867</v>
+        <v>0.9743288990222393</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.646845787427258e-05</v>
+        <v>1.558738314970903e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.003236165270209312</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.419600108904289</v>
+        <v>0.9743257381850103</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.997732826962944e-05</v>
+        <v>4.990931307851776e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.003123234957456589</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.419593562881174</v>
+        <v>0.9743200894633627</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.034975653315254e-05</v>
+        <v>1.395731888813558e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.003286231309175491</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.419595553992971</v>
+        <v>0.9743181659872784</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.993667665820105e-06</v>
+        <v>-1.503166167089948e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.003528227098286152</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.419589067766295</v>
+        <v>0.974312479709693</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-1.911892527543644e-06</v>
+        <v>-3.970630842514548e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.003647989593446255</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.419583109168156</v>
+        <v>0.9743070692397754</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-2.77474353817759e-06</v>
+        <v>-3.887371769088796e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.003686519339680672</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.419578439899519</v>
+        <v>0.974302234605457</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.031182895915095e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.003631375730037689</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.419573150751957</v>
+        <v>0.9743020906215494</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.003515692427754402</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.419573128017656</v>
+        <v>0.974302067887248</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.003438230603933334</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.419573446297872</v>
+        <v>0.9743023861674648</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.003578027710318565</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.419574537544329</v>
+        <v>0.9743034774139216</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.004015266895294189</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.419573847937193</v>
+        <v>0.9743027878067857</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.004483098164200783</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.419573878249595</v>
+        <v>0.9743028181191874</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.004764264449477196</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.419573688797084</v>
+        <v>0.9743026286666773</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.004885663278400898</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.419573741843787</v>
+        <v>0.9743026817133802</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.004918212071061134</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.419573794890491</v>
+        <v>0.974302734760083</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.00484969187527895</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.419573756999988</v>
+        <v>0.974302696869581</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.004694512113928795</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.419573628172281</v>
+        <v>0.9743025680418743</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.004485498182475567</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.419573484188374</v>
+        <v>0.9743024240579667</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.004253833554685116</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.419573325048265</v>
+        <v>0.9743022649178584</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.004059065133333206</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.419573378094968</v>
+        <v>0.9743023179645612</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.003908995538949966</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.16</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.419573325048265</v>
+        <v>0.9743022649178584</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.003775482997298241</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.419573325048265</v>
+        <v>0.9743022649178584</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.003604027442634106</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.419573143173856</v>
+        <v>0.9743020830434489</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.003519223071634769</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.419573309892065</v>
+        <v>0.9743022497616576</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.003560183569788933</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.419573506922675</v>
+        <v>0.974302446792268</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.003589963540434837</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.419573347782567</v>
+        <v>0.9743022876521595</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.003573991358280182</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.419573385673069</v>
+        <v>0.9743023255426616</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.003599180839955807</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.419573582703679</v>
+        <v>0.9743025225732718</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.003692455589771271</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.419573559969378</v>
+        <v>0.9743024998389705</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.003748656250536442</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.16</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.41957340840737</v>
+        <v>0.9743023482769627</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.003736778162419796</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.419573332626366</v>
+        <v>0.9743022724959587</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.003712901845574379</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.419573431141671</v>
+        <v>0.9743023710112639</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.003673200495541096</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.419573438719772</v>
+        <v>0.9743023785893642</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.003723007626831532</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.3</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.419573703953286</v>
+        <v>0.9743026438228781</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.003759969025850296</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.41957340840737</v>
+        <v>0.9743023482769627</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.003800345584750175</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.3</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.419573650906583</v>
+        <v>0.9743025907761755</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.003916368819773197</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.419573734265687</v>
+        <v>0.9743026741352798</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.003902341239154339</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.3</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.419573567547478</v>
+        <v>0.9743025074170711</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.004016357474029064</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.3</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.419573756999988</v>
+        <v>0.974302696869581</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.004061607643961906</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.41957340840737</v>
+        <v>0.9743023482769627</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.004014709964394569</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.419573203798659</v>
+        <v>0.9743021436682521</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.003905048593878746</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.419573317470165</v>
+        <v>0.9743022573397581</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.003777582198381424</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.419573332626366</v>
+        <v>0.9743022724959587</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.003606715239584446</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.419573097705254</v>
+        <v>0.9743020375748466</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.003478522412478924</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.419573158330057</v>
+        <v>0.9743020981996497</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.003336024470627308</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.419573029502351</v>
+        <v>0.974301969371943</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.003202524967491627</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.419573165908157</v>
+        <v>0.97430210577775</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.003236796706914902</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.419573340204467</v>
+        <v>0.9743022800740593</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.0033426433801651</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.419573484188374</v>
+        <v>0.9743024240579667</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.003396743908524513</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.419573317470165</v>
+        <v>0.9743022573397581</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.003427703864872456</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.419573309892065</v>
+        <v>0.9743022497616576</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.003362786024808884</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.41957302192425</v>
+        <v>0.9743019617938425</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.003252764232456684</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.419573037080451</v>
+        <v>0.9743019769500434</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.003206214867532253</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.419573264423462</v>
+        <v>0.9743022042930553</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.003176196478307247</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.419573249267262</v>
+        <v>0.9743021891368544</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.003231591545045376</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.419573355360667</v>
+        <v>0.9743022952302599</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.003212861716747284</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.419573082549053</v>
+        <v>0.9743020224186457</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.003174219280481339</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.419573181064358</v>
+        <v>0.9743021209339509</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.003187635913491249</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.419573332626366</v>
+        <v>0.9743022724959587</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.003226322121918201</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.419573347782567</v>
+        <v>0.9743022876521595</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.003265945240855217</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.16</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.419573325048265</v>
+        <v>0.9743022649178584</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.003310487605631351</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.3</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.41957340840737</v>
+        <v>0.9743023482769627</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.003396171145141125</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.3</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.419573506922675</v>
+        <v>0.974302446792268</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.003444540314376354</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.3</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.419573340204467</v>
+        <v>0.9743022800740593</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.003437195904552937</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.3</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.419573325048265</v>
+        <v>0.9743022649178584</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.003403989598155022</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.16</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.419573294735864</v>
+        <v>0.974302234605457</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.003362292423844337</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.16</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.419573279579663</v>
+        <v>0.9743022194492561</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.003340002149343491</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.419573317470165</v>
+        <v>0.9743022573397581</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.003327394835650921</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.419573332626366</v>
+        <v>0.9743022724959587</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.003320246934890747</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.419573325048265</v>
+        <v>0.9743022649178584</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_1_000007.xlsx
+++ b/out/LSTM-Mamba1_repeat_1_000007.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.007550928276032209</v>
+        <v>-0.007550936657935381</v>
       </c>
       <c r="JB2" t="n">
         <v>-1.28</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.004569283686578274</v>
+        <v>-0.004569301381707191</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.8599999999999997</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.002942008897662163</v>
+        <v>-0.002942025661468506</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.4399999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.002032063901424408</v>
+        <v>-0.002032076008617878</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.16</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.001496887765824795</v>
+        <v>-0.001496897079050541</v>
       </c>
       <c r="JB6" t="n">
         <v>0.7199999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.001181662082672119</v>
+        <v>-0.001181667670607567</v>
       </c>
       <c r="JB7" t="n">
         <v>0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.0009840475395321846</v>
+        <v>-0.0009840652346611023</v>
       </c>
       <c r="JB8" t="n">
         <v>0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.0008318424224853516</v>
+        <v>-0.0008318508043885231</v>
       </c>
       <c r="JB9" t="n">
         <v>0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.0006994428113102913</v>
+        <v>-0.0006994465366005898</v>
       </c>
       <c r="JB10" t="n">
         <v>0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.0005995491519570351</v>
+        <v>-0.0005995556712150574</v>
       </c>
       <c r="JB11" t="n">
         <v>0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.0005179233849048615</v>
+        <v>-0.0005179261788725853</v>
       </c>
       <c r="JB12" t="n">
         <v>0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.0004509929567575455</v>
+        <v>-0.000450989231467247</v>
       </c>
       <c r="JB13" t="n">
         <v>0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.0003774473443627357</v>
+        <v>-0.0003774650394916534</v>
       </c>
       <c r="JB14" t="n">
         <v>0.9999999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.0003381473943591118</v>
+        <v>-0.0003381641581654549</v>
       </c>
       <c r="JB15" t="n">
         <v>0.9999999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.0002913353964686394</v>
+        <v>-0.0002913493663072586</v>
       </c>
       <c r="JB16" t="n">
         <v>0.3999999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.0002347761765122414</v>
+        <v>-0.0002347715198993683</v>
       </c>
       <c r="JB17" t="n">
         <v>0.3999999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.0001595616340637207</v>
+        <v>-0.0001595597714185715</v>
       </c>
       <c r="JB18" t="n">
         <v>0.3999999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.0001011621206998825</v>
+        <v>-0.0001011677086353302</v>
       </c>
       <c r="JB19" t="n">
         <v>0.3999999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>5.280692130327225e-05</v>
+        <v>5.279947072267532e-05</v>
       </c>
       <c r="JB21" t="n">
         <v>0.3999999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.0001017004251480103</v>
+        <v>0.0001016603782773018</v>
       </c>
       <c r="JB22" t="n">
         <v>0.3999999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.0001066382974386215</v>
+        <v>0.0001066243276000023</v>
       </c>
       <c r="JB23" t="n">
         <v>0.2599999999999998</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-5.587935447692871e-08</v>
+        <v>-9.96515154838562e-08</v>
       </c>
       <c r="JB24" t="n">
         <v>0.1199999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.0001111077144742012</v>
+        <v>-0.0001111412420868874</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.02000000000000007</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.0001940708607435226</v>
+        <v>-0.0001941006630659103</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.16</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.0002483353018760681</v>
+        <v>-0.0002483567222952843</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.3</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.0002760998904705048</v>
+        <v>-0.0002761222422122955</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.3</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.0002594385296106339</v>
+        <v>-0.0002594580873847008</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.3</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.000296187587082386</v>
+        <v>-0.0002962052822113037</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.3</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.0003367029130458832</v>
+        <v>-0.0003367206081748009</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.3</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.0003795046359300613</v>
+        <v>-0.0003795167431235313</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.3</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.0004108911380171776</v>
+        <v>-0.000410902313888073</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.3</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.0004037357866764069</v>
+        <v>-0.0004037348553538322</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.3</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.0003892546519637108</v>
+        <v>-0.0003892621025443077</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.3</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.0003645466640591621</v>
+        <v>-0.0003645531833171844</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.4399999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.0003487421199679375</v>
+        <v>-0.0003487458452582359</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.5799999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.0005714474245905876</v>
+        <v>-0.0005714613944292068</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.7199999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.0008577350527048111</v>
+        <v>-0.0008577322587370872</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.8599999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.001155446283519268</v>
+        <v>-0.001155432313680649</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.9999999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.001379312016069889</v>
+        <v>-0.001379308290779591</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.001551940105855465</v>
+        <v>-0.001551938243210316</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.001666946336627007</v>
+        <v>-0.001666942611336708</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.001851177774369717</v>
+        <v>-0.001851164735853672</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.00222381018102169</v>
+        <v>-0.00222382415086031</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.002675746567547321</v>
+        <v>-0.002675735391676426</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.003212705254554749</v>
+        <v>-0.003212699666619301</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.003545243293046951</v>
+        <v>-0.003545223735272884</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.003660714253783226</v>
+        <v>-0.003660698421299458</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.003669597208499908</v>
+        <v>-0.003669583238661289</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.003657129593193531</v>
+        <v>-0.003657088615000248</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.003572961315512657</v>
+        <v>-0.003572937101125717</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.003445684909820557</v>
+        <v>-0.003445656038820744</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.003341276198625565</v>
+        <v>-0.003341253846883774</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.003245980478823185</v>
+        <v>-0.003245965577661991</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.003205060958862305</v>
+        <v>-0.003205043263733387</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.003236165270209312</v>
+        <v>-0.003236162476241589</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.003123234957456589</v>
+        <v>-0.003123224712908268</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.003286231309175491</v>
+        <v>-0.003286213614046574</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.003528227098286152</v>
+        <v>-0.003528190776705742</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.003647989593446255</v>
+        <v>-0.003647962585091591</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.003686519339680672</v>
+        <v>-0.003686502575874329</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.003631375730037689</v>
+        <v>-0.003631348721683025</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.003515692427754402</v>
+        <v>-0.003515663556754589</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.003438230603933334</v>
+        <v>-0.003438223153352737</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.9999999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.003578027710318565</v>
+        <v>-0.003578009083867073</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.9999999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.004015266895294189</v>
+        <v>-0.004015258513391018</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.9999999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.004483098164200783</v>
+        <v>-0.004483072087168694</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.9999999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.004764264449477196</v>
+        <v>-0.004764185287058353</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.004885663278400898</v>
+        <v>-0.00488560926169157</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.004918212071061134</v>
+        <v>-0.00491818506270647</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.00484969187527895</v>
+        <v>-0.004849673248827457</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.004694512113928795</v>
+        <v>-0.004694485105574131</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.004485498182475567</v>
+        <v>-0.004485480487346649</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.004253833554685116</v>
+        <v>-0.004253805615007877</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.2599999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.004059065133333206</v>
+        <v>-0.00405903160572052</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.1199999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.003908995538949966</v>
+        <v>-0.003908977843821049</v>
       </c>
       <c r="JB77" t="n">
         <v>0.16</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.003775482997298241</v>
+        <v>-0.003775469958782196</v>
       </c>
       <c r="JB78" t="n">
         <v>0.4399999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.003604027442634106</v>
+        <v>-0.003603998571634293</v>
       </c>
       <c r="JB79" t="n">
         <v>0.7199999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.003519223071634769</v>
+        <v>-0.003519205376505852</v>
       </c>
       <c r="JB80" t="n">
         <v>0.8599999999999999</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.003560183569788933</v>
+        <v>-0.00356016680598259</v>
       </c>
       <c r="JB81" t="n">
         <v>0.9999999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.003589963540434837</v>
+        <v>-0.003589959815144539</v>
       </c>
       <c r="JB82" t="n">
         <v>0.9999999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.003573991358280182</v>
+        <v>-0.003573962487280369</v>
       </c>
       <c r="JB83" t="n">
         <v>0.8599999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.003599180839955807</v>
+        <v>-0.003599165938794613</v>
       </c>
       <c r="JB84" t="n">
         <v>0.7199999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.003692455589771271</v>
+        <v>-0.00369243323802948</v>
       </c>
       <c r="JB85" t="n">
         <v>0.5799999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.003748656250536442</v>
+        <v>-0.003748609684407711</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.16</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.003736778162419796</v>
+        <v>-0.003736734390258789</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.3</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.003712901845574379</v>
+        <v>-0.003712866455316544</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.3</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.003673200495541096</v>
+        <v>-0.003673186525702477</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.3</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.003723007626831532</v>
+        <v>-0.003722989000380039</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.3</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.003759969025850296</v>
+        <v>-0.003759943880140781</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.3</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.003800345584750175</v>
+        <v>-0.003800331614911556</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.3</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.003916368819773197</v>
+        <v>-0.003916352055966854</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.3</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.003902341239154339</v>
+        <v>-0.003902312368154526</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.3</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.004016357474029064</v>
+        <v>-0.004016323015093803</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.3</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.004061607643961906</v>
+        <v>-0.004061594605445862</v>
       </c>
       <c r="JB96" t="n">
         <v>0.4399999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.004014709964394569</v>
+        <v>-0.004014682024717331</v>
       </c>
       <c r="JB97" t="n">
         <v>0.5799999999999998</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.003905048593878746</v>
+        <v>-0.003905035555362701</v>
       </c>
       <c r="JB98" t="n">
         <v>0.7199999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.003777582198381424</v>
+        <v>-0.003777574747800827</v>
       </c>
       <c r="JB99" t="n">
         <v>0.8599999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.003606715239584446</v>
+        <v>-0.003606707789003849</v>
       </c>
       <c r="JB100" t="n">
         <v>0.9999999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.003478522412478924</v>
+        <v>-0.003478497266769409</v>
       </c>
       <c r="JB101" t="n">
         <v>0.9999999999999998</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.003336024470627308</v>
+        <v>-0.003335991874337196</v>
       </c>
       <c r="JB102" t="n">
         <v>0.9999999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.003202524967491627</v>
+        <v>-0.003202498890459538</v>
       </c>
       <c r="JB103" t="n">
         <v>0.9999999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.003236796706914902</v>
+        <v>-0.003236773423850536</v>
       </c>
       <c r="JB104" t="n">
         <v>0.9999999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.0033426433801651</v>
+        <v>-0.003342629410326481</v>
       </c>
       <c r="JB105" t="n">
         <v>0.8599999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.003396743908524513</v>
+        <v>-0.003396746702492237</v>
       </c>
       <c r="JB106" t="n">
         <v>0.1199999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.003427703864872456</v>
+        <v>-0.003427682444453239</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.02000000000000007</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.003362786024808884</v>
+        <v>-0.003362780436873436</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.02000000000000007</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.003252764232456684</v>
+        <v>-0.003252745606005192</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.02000000000000007</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.003206214867532253</v>
+        <v>-0.003206209279596806</v>
       </c>
       <c r="JB110" t="n">
         <v>0.1199999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.003176196478307247</v>
+        <v>-0.003176189959049225</v>
       </c>
       <c r="JB111" t="n">
         <v>0.2599999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.003231591545045376</v>
+        <v>-0.003231590613722801</v>
       </c>
       <c r="JB112" t="n">
         <v>0.9999999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.003212861716747284</v>
+        <v>-0.003212867304682732</v>
       </c>
       <c r="JB113" t="n">
         <v>0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.003187635913491249</v>
+        <v>-0.003187624737620354</v>
       </c>
       <c r="JB115" t="n">
         <v>0.7199999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.003226322121918201</v>
+        <v>-0.003226317465305328</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.02000000000000007</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.003265945240855217</v>
+        <v>-0.003265930339694023</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.16</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.003310487605631351</v>
+        <v>-0.00331047922372818</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.3</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.003396171145141125</v>
+        <v>-0.003396179527044296</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.3</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.003444540314376354</v>
+        <v>-0.003444547764956951</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.3</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.003437195904552937</v>
+        <v>-0.003437207080423832</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.3</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.003403989598155022</v>
+        <v>-0.003403995186090469</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.16</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.003362292423844337</v>
+        <v>-0.003362290561199188</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.16</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.003340002149343491</v>
+        <v>-0.003340003080666065</v>
       </c>
       <c r="JB124" t="n">
         <v>0.4399999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.003327394835650921</v>
+        <v>-0.003327391110360622</v>
       </c>
       <c r="JB125" t="n">
         <v>0.4399999999999999</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.003320246934890747</v>
+        <v>-0.003320242278277874</v>
       </c>
       <c r="JB126" t="n">
         <v>0.4399999999999999</v>
